--- a/Math/Calculus/Calculation/FunctionSampler/resources/抽象函数.xlsx
+++ b/Math/Calculus/Calculation/FunctionSampler/resources/抽象函数.xlsx
@@ -4,10 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="二元组合" sheetId="2" r:id="rId1"/>
+    <sheet name="三元组合" sheetId="3" r:id="rId2"/>
+    <sheet name="一元运算" sheetId="6" r:id="rId3"/>
+    <sheet name="二元运算" sheetId="7" r:id="rId4"/>
+    <sheet name="原始数据" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,14 +31,1112 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2331" uniqueCount="477">
+  <si>
+    <t>二元组合</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）+连续性（一元）</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）+极限存在（一元）</t>
+  </si>
+  <si>
+    <t>连续性（一元）+极限存在（一元）</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+可微性（多元）</t>
+  </si>
+  <si>
+    <t>00：</t>
+  </si>
+  <si>
+    <t>Piecewise((1, x &gt;= 0), (-1, x &lt; 0))</t>
+  </si>
+  <si>
+    <t>Piecewise((sin(1/x), Ne(x, 0)), (0, Eq(x, 0)))</t>
+  </si>
+  <si>
+    <t>abs(x) + abs(y)</t>
+  </si>
+  <si>
+    <t>01：</t>
+  </si>
+  <si>
+    <t>abs(x)</t>
+  </si>
+  <si>
+    <t>Piecewise((abs(x), Ne(x, 0)), (1, Eq(x, 0)))</t>
+  </si>
+  <si>
+    <t>Piecewise((x, Ne(x, 0)), (1, Eq(x, 0)))</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>10：</t>
+  </si>
+  <si>
+    <t>Piecewise(((x**2*y)/(x**4 + y**2), Or(Ne(x, 0), Ne(y, 0))), (0, And(Eq(x, 0), Eq(y, 0))))</t>
+  </si>
+  <si>
+    <t>11：</t>
+  </si>
+  <si>
+    <t>x**2</t>
+  </si>
+  <si>
+    <t>x**3</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>x**2 + y**2</t>
+  </si>
+  <si>
+    <t>三元组合</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）+连续性（一元）+极限存在（一元）</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+可微性（多元）+连续性（多元）</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+可微性（多元）+二阶偏导连续（多元）</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）+连续性（多元）+二阶偏导连续（多元）</t>
+  </si>
+  <si>
+    <t>可微性（多元）+连续性（多元）+二阶偏导连续（多元）</t>
+  </si>
+  <si>
+    <t>000：</t>
+  </si>
+  <si>
+    <t>Piecewise((1/x, Ne(x, 0)), (0, Eq(x, 0)))</t>
+  </si>
+  <si>
+    <t>Piecewise((1, Ne(x*y, 0)), (0, Eq(x*y, 0)))</t>
+  </si>
+  <si>
+    <t>Piecewise((1, x**2 + y**2 &gt;= 1), (0, x**2 + y**2 &lt; 1))</t>
+  </si>
+  <si>
+    <t>001：</t>
+  </si>
+  <si>
+    <t>010：</t>
+  </si>
+  <si>
+    <t>011：</t>
+  </si>
+  <si>
+    <t>100：</t>
+  </si>
+  <si>
+    <t>101：</t>
+  </si>
+  <si>
+    <t>sqrt(abs(x*y))</t>
+  </si>
+  <si>
+    <t>110：</t>
+  </si>
+  <si>
+    <t>Piecewise(((x**2*y**2)*sin(1/(x**2 + y**2)), Or(Ne(x, 0), Ne(y, 0))), (0, And(Eq(x, 0), Eq(y, 0))))</t>
+  </si>
+  <si>
+    <t>Piecewise(((x**2*y**2)*sin(1/(x**2 + y**2)), Ne(x**2 + y**2, 0)), (0, And(Eq(x, 0), Eq(y, 0))))</t>
+  </si>
+  <si>
+    <t>111：</t>
+  </si>
+  <si>
+    <t>x**3 + y**3</t>
+  </si>
+  <si>
+    <t>一阶或二阶可导（一元）：f(x)在区间区间(a,b)内具有k阶导数</t>
+  </si>
+  <si>
+    <t>偏导数存在（多元）：f(x,y)在趋区域D内存在一阶偏导fx(x,y)和fy(x,y)，且D内处处可求偏导</t>
+  </si>
+  <si>
+    <t>连续性（一元）：f(x)在开（闭）区间a到b上连续</t>
+  </si>
+  <si>
+    <t>可微性（多元）：f(x,y)在点(x0,y0)处可微，满足可微的极限定义式等于0</t>
+  </si>
+  <si>
+    <t>极限存在（一元）：f(x)在x趋于x0时极限存在，且极限等于A</t>
+  </si>
+  <si>
+    <t>连续性（多元）：f(x,y)在区域D上连续，D内任意点处f(x,y)的极限等于f(x,y)在该点处的函数值</t>
+  </si>
+  <si>
+    <t>周期性（一元）：f(x)是以T为周期的周期函数，满足f(x+T)=f(x)</t>
+  </si>
+  <si>
+    <t>可定积分（一元）：f(x)在开（闭）区间a到b上可积，且定积分值等于常数k</t>
+  </si>
+  <si>
+    <t>二阶偏导连续（多元）：f(x,y)在区域D内的二阶偏导数均连续，满足fxy(x,y)=fyx(x,y)（混合偏导相等）</t>
+  </si>
+  <si>
+    <t>奇函数（一元）：f(x)在定义域内满足f(-x)=-f(x)</t>
+  </si>
+  <si>
+    <t>偶函数（一元）：f(x)在定义域内满足f(-x)=f(x)</t>
+  </si>
+  <si>
+    <t>相切（一元）：f(x)在点(x0,f(x0))处与直线y=kx+b相切</t>
+  </si>
+  <si>
+    <t>反常积分收敛（一元）：被积函数为f(x)的无穷积分/瑕积分（若无瑕点，则在无穷限上积分）收敛到常数C</t>
+  </si>
+  <si>
+    <t>相反数（-f(x)=g(x)或-f(x,y)=g(x,y)）</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>abs(x)+abs(y)</t>
+  </si>
+  <si>
+    <t>Piecewise((1,x&gt;=0),(-1,x&lt;0))</t>
+  </si>
+  <si>
+    <t>Piecewise((sin(1/x),Ne(x,0)),(0,Eq(x,0)))</t>
+  </si>
+  <si>
+    <t>Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))</t>
+  </si>
+  <si>
+    <t>x+1</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=分段函数{1,x为有理数；0,x为无理数}</t>
+  </si>
+  <si>
+    <t>(x**2*y)/(x**4 + y**2)</t>
+  </si>
+  <si>
+    <t>x**2+1</t>
+  </si>
+  <si>
+    <t>Piecewise((1,x&gt;=0),(0,x&lt;0))</t>
+  </si>
+  <si>
+    <t>x + y</t>
+  </si>
+  <si>
+    <t>sin(x)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1/x**2</t>
+  </si>
+  <si>
+    <t>绝对值（|f(x)|=g(x)或|f(x,y)|=g(x,y)）</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=分段{1,x≥0;-1,x&lt;0}</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数</t>
+  </si>
+  <si>
+    <t>abs(x+1)</t>
+  </si>
+  <si>
+    <t>Piecewise((x,x&gt;=0),(2*x,x&lt;0))</t>
+  </si>
+  <si>
+    <t>1/x</t>
+  </si>
+  <si>
+    <t>Piecewise(((x**2*y)/(x**4 + y**2),Ne(x,0)),(0,Eq(x,0)))</t>
+  </si>
+  <si>
+    <t>Piecewise((exp(x),x&gt;=0),(-exp(x),x&lt;0))</t>
+  </si>
+  <si>
+    <t>abs(x)**3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>sin(x)/x</t>
+  </si>
+  <si>
+    <t>x**2+y**2</t>
+  </si>
+  <si>
+    <t>abs(x+y)</t>
+  </si>
+  <si>
+    <t>x**4+y**4</t>
+  </si>
+  <si>
+    <t>exp(-x**2)</t>
+  </si>
+  <si>
+    <t>取倒数（1/f(x)=g(x)或1/f(x,y)=g(x,y)）</t>
+  </si>
+  <si>
+    <t>Piecewise((1, x &gt;= 0), (0, x &lt; 0))</t>
+  </si>
+  <si>
+    <t>Piecewise(((x**2 + y**2), Or(x &gt; 0, x &lt; 0) | Or(y &gt; 0, y &lt; 0)), (0, x == 0 &amp; y == 0))</t>
+  </si>
+  <si>
+    <t>Piecewise((sin(1/x), Or(x &gt; 0, x &lt; 0)), (0, x == 0))</t>
+  </si>
+  <si>
+    <t>Piecewise((1, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (0, x == 0 | y == 0))</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;无定义，x∉Q}（不可积）</t>
+  </si>
+  <si>
+    <t>(x**2*y)/(x**4+y**2)</t>
+  </si>
+  <si>
+    <t>x**2+y**2+1</t>
+  </si>
+  <si>
+    <t>1/x**2@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>平方（f(x)²=g(x)或f(x,y)²=g(x,y)）</t>
+  </si>
+  <si>
+    <t>Piecewise((x, Or(x&gt;0,x&lt;0)), (1, x==0))</t>
+  </si>
+  <si>
+    <t>Piecewise((sin(1/x), Or(x&gt;0,x&lt;0)), (0, x==0))</t>
+  </si>
+  <si>
+    <t>Piecewise((1, Or(x&gt;0,x&lt;0) &amp; Or(y&gt;0,y&lt;0)), (0, x==0 | y==0))</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）</t>
+  </si>
+  <si>
+    <t>Piecewise((x, x &gt;= 0), (2*x, x &lt; 0))</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>Piecewise((1, x&gt;0), (-1, x&lt;0), (0, x==0))</t>
+  </si>
+  <si>
+    <t>Piecewise((2, Or(x&gt;0,x&lt;0) &amp; Or(y&gt;0,y&lt;0)), (0, x==0 | y==0))</t>
+  </si>
+  <si>
+    <t>abs(sin(x))</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=分段{1,x∈Q;-1,x∉Q}（不可积）</t>
+  </si>
+  <si>
+    <t>x+y</t>
+  </si>
+  <si>
+    <t>exp(-x)</t>
+  </si>
+  <si>
+    <t>立方（f(x)³=g(x)或f(x,y)³=g(x,y)）</t>
+  </si>
+  <si>
+    <t>Piecewise((1, x &gt; 0), (-1, x &lt; 0), (0, x == 0))</t>
+  </si>
+  <si>
+    <t>Piecewise((2, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (0, x == 0 | y == 0))</t>
+  </si>
+  <si>
+    <t>平方根（sqrt(f(x))=g(x)或sqrt(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>Piecewise((sin(1/x)**2, Or(x &gt; 0, x &lt; 0)), (0, x == 0))</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）;分段{1,x∈Q;0,x∉Q}（不可积）</t>
+  </si>
+  <si>
+    <t>(x**2*y**2)/(x**4+y**4)</t>
+  </si>
+  <si>
+    <t>Piecewise((x**2, x &gt;= 0), (2*x**2, x &lt; 0))</t>
+  </si>
+  <si>
+    <t>1/x**4@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>立方根（curt(f(x))=g(x)或curt(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>Piecewise((1, (Or(x &gt; 0, x &lt; 0)) &amp; (Or(y &gt; 0, y &lt; 0))), (0, x == 0 | y == 0))</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;0,x∉Q}（不可积）</t>
+  </si>
+  <si>
+    <t>1/x**3@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**6+y**6</t>
+  </si>
+  <si>
+    <t>x**6</t>
+  </si>
+  <si>
+    <t>1/x**6@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**3+y**3</t>
+  </si>
+  <si>
+    <t>exp(-3x)</t>
+  </si>
+  <si>
+    <t>向上取整（ceil(f(x))=g(x)或ceil(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>Piecewise((1 - abs(x*y), (x*y &gt; 0) | (x*y &lt; 0)), (0, x == 0 &amp; y == 0))</t>
+  </si>
+  <si>
+    <t>x + sin(x)</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=分段{1.5,x∈Q;1,x∉Q}（不可积，不满足性质H）</t>
+  </si>
+  <si>
+    <t>(x**2*y)/(x**4+y**2)+1</t>
+  </si>
+  <si>
+    <t>Piecewise((2.2, x &lt; 0), (2.8, x &gt;= 0))</t>
+  </si>
+  <si>
+    <t>Piecewise((0.5, x &lt; 0), (1.5, x &gt;= 0))</t>
+  </si>
+  <si>
+    <t>Piecewise((0.5, x*y &lt; 0), (1.5, x*y &gt;= 0))</t>
+  </si>
+  <si>
+    <t>abs(0.5*sin(x))+0.5</t>
+  </si>
+  <si>
+    <t>1/x+1@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>向下取整（floor(f(x))=g(x)或floor(f(x,y))=g(x,y)）</t>
+  </si>
+  <si>
+    <t>Piecewise((1 - abs(x*y), Or(x*y &gt; 0, x*y &lt; 0)), (0, x*y == 0))</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;分段{1.5,x∈Q;1,x∉Q};1</t>
+  </si>
+  <si>
+    <t>abs(x)+0.5</t>
+  </si>
+  <si>
+    <t>Piecewise((0.5, x*y &lt; 0), (0.25, x*y &gt;= 0))</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）;1</t>
+  </si>
+  <si>
+    <t>Piecewise((1.5, x &gt; 0), (0.5, x == 0), (-0.5, x &lt; 0))</t>
+  </si>
+  <si>
+    <t>Piecewise((0, Or(x &gt; 1, x &lt; 1)), (0.5, x == 1))</t>
+  </si>
+  <si>
+    <t>x+0.5</t>
+  </si>
+  <si>
+    <t>加减（f(x)±g(x)=h(x)或f(x,y)±g(x,y)=h(x,y)）</t>
+  </si>
+  <si>
+    <t>abs(x);abs(x)</t>
+  </si>
+  <si>
+    <t>abs(x)+abs(y);abs(x)+abs(y)</t>
+  </si>
+  <si>
+    <t>1/x;1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/sqrt(x**2+y**2);1/sqrt(x**2+y**2)</t>
+  </si>
+  <si>
+    <t>1/(x+y);1/(x+y)@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>sin(x)+1/x;cos(x)+1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x;x@(x&gt;=0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>1/(x+y);y@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2+1;x**2+1</t>
+  </si>
+  <si>
+    <t>x+1;x+1</t>
+  </si>
+  <si>
+    <t>1/x;1/x**2@x&gt;=1</t>
+  </si>
+  <si>
+    <t>x;2*x;3*x</t>
+  </si>
+  <si>
+    <t>x+y;x*y;x+y-x*y</t>
+  </si>
+  <si>
+    <t>sin(x);x</t>
+  </si>
+  <si>
+    <t>x**2;cos(x)</t>
+  </si>
+  <si>
+    <t>x+1;2*x</t>
+  </si>
+  <si>
+    <t>sin(x);sin(sqrt(2)*x)</t>
+  </si>
+  <si>
+    <t>x;1</t>
+  </si>
+  <si>
+    <t>x**2;y**2;x**2+y**2</t>
+  </si>
+  <si>
+    <t>x;x**3</t>
+  </si>
+  <si>
+    <t>1/x**2;1/x**3@x&gt;=1</t>
+  </si>
+  <si>
+    <t>sin(x);cos(x)</t>
+  </si>
+  <si>
+    <t>2*x+1;-x;x+1</t>
+  </si>
+  <si>
+    <t>abs(x);x</t>
+  </si>
+  <si>
+    <t>abs(x);y</t>
+  </si>
+  <si>
+    <t>1/x;x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/sqrt(x**2+y**2);y</t>
+  </si>
+  <si>
+    <t>sin(x)+1/x;sin(x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2+1;x</t>
+  </si>
+  <si>
+    <t>x+1;x**2</t>
+  </si>
+  <si>
+    <t>x;x**2</t>
+  </si>
+  <si>
+    <t>x*y;x**2*y</t>
+  </si>
+  <si>
+    <t>sin(x);sin(x)</t>
+  </si>
+  <si>
+    <t>x;x**2@(x&gt;=0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>x**2;x**4</t>
+  </si>
+  <si>
+    <t>sin(x);sin(2*x)</t>
+  </si>
+  <si>
+    <t>乘法（f(x)*g(x)=h(x)或f(x,y)*g(x,y)=h(x,y)）</t>
+  </si>
+  <si>
+    <t>abs(x)+1;abs(x)+1</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/(x+y)@Or(x+y&gt;0,x+y&lt;0);1/(x+y)@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>sin(x)+1/x@Or(x&gt;0,x&lt;0);cos(x)+1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);1/x@(x&gt;=0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>1/sqrt(x)@x&gt;=1;1/sqrt(x)@x&gt;=1</t>
+  </si>
+  <si>
+    <t>x;2*x;2*x**2</t>
+  </si>
+  <si>
+    <t>x+y;x*y;(x+y)*x*y</t>
+  </si>
+  <si>
+    <t>x**2;y**2;x**2*y**2</t>
+  </si>
+  <si>
+    <t>1/x**2@x&gt;=1;1/x**3@x&gt;=1</t>
+  </si>
+  <si>
+    <t>2*x+1;-x;-2*x**2-x</t>
+  </si>
+  <si>
+    <t>x;abs(x)</t>
+  </si>
+  <si>
+    <t>0;abs(x)</t>
+  </si>
+  <si>
+    <t>0;1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>0;abs(x)+abs(y)</t>
+  </si>
+  <si>
+    <t>x;1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>0;1/(x+y)@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>0;x</t>
+  </si>
+  <si>
+    <t>0;1/x@(x&gt;=0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>0;x@x&gt;=1</t>
+  </si>
+  <si>
+    <t>x;x**2*y</t>
+  </si>
+  <si>
+    <t>x;x**2@x&gt;=1</t>
+  </si>
+  <si>
+    <t>x;x</t>
+  </si>
+  <si>
+    <t>x;y</t>
+  </si>
+  <si>
+    <t>x**2;x**3</t>
+  </si>
+  <si>
+    <t>除法（f(x)/g(x)=h(x)或f(x,y)/g(x,y)=h(x,y)）</t>
+  </si>
+  <si>
+    <t>x**2;x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2*y;x*y@Or(x*y&gt;0,x*y&lt;0)</t>
+  </si>
+  <si>
+    <t>x+1;1</t>
+  </si>
+  <si>
+    <t>x**2+y**2;1</t>
+  </si>
+  <si>
+    <t>x**3;x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x+y;2</t>
+  </si>
+  <si>
+    <t>sin(2*x);sin(x)@Or(sin(x)&gt;0,sin(x)&lt;0)</t>
+  </si>
+  <si>
+    <t>1;2@(x&gt;=0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>x**3*y**3;x*y@Or(x*y&gt;0,x*y&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x**2;1@x&gt;=1</t>
+  </si>
+  <si>
+    <t>abs(x);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>abs(x);y@Or(y&gt;0,y&lt;0)</t>
+  </si>
+  <si>
+    <t>sign(x);1</t>
+  </si>
+  <si>
+    <t>abs(x)+abs(y);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/abs(x+y);1</t>
+  </si>
+  <si>
+    <t>x+abs(x);sin(x)@Or(sin(x)&gt;0,sin(x)&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);1@(x&gt;0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>abs(x)+abs(y);y@Or(y&gt;0,y&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2+abs(x);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x@x&gt;=1;1/x**2@x&gt;=1</t>
+  </si>
+  <si>
+    <t>x;abs(x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x;1/sqrt(x**2+y**2)@Or(x**2+y**2&gt;0,x**2+y**2&lt;0)</t>
+  </si>
+  <si>
+    <t>x**3;x**2@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x;1/(x+y)@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>sin(x);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x;1@(x&gt;=0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>x**4;x**2@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2*y**3;x*y**2@Or(x*y&gt;0,x*y&lt;0)</t>
+  </si>
+  <si>
+    <t>sin(x);cos(x)@Or(cos(x)&gt;0,cos(x)&lt;0)</t>
+  </si>
+  <si>
+    <t>x+y;x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2+1;x+1@Or(x+1&gt;0,x+1&lt;0)</t>
+  </si>
+  <si>
+    <t>1/sqrt(x**2+y**2);1/(x+y)@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>x+abs(x);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2;x@(x&gt;0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>x**3+y**3;x+y@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>x**4;x**3@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>exp(x);exp(x)</t>
+  </si>
+  <si>
+    <t>x**2;abs(x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**3;x*abs(x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>sin(x);abs(sin(x))@Or(sin(x)&gt;0,sin(x)&lt;0)</t>
+  </si>
+  <si>
+    <t>x**4;x**2*abs(x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>exp(x);exp(abs(x))</t>
+  </si>
+  <si>
+    <t>1/x@x&gt;=1;1/abs(x)@x&gt;=1</t>
+  </si>
+  <si>
+    <t>x**3;sqrt(abs(x))</t>
+  </si>
+  <si>
+    <t>x**3*y;sqrt(abs(x))+y</t>
+  </si>
+  <si>
+    <t>1;1/x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2+y**2;abs(x)+abs(y)</t>
+  </si>
+  <si>
+    <t>x;sin(1/x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1;1/(x+y)@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>x**4*y**2;abs(x)*y**2</t>
+  </si>
+  <si>
+    <t>x**3;x**2</t>
+  </si>
+  <si>
+    <t>x**4;sqrt(abs(x))</t>
+  </si>
+  <si>
+    <t>1/x**2;1/sqrt(x)@x&gt;0</t>
+  </si>
+  <si>
+    <t>1;x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x;y@Or(y&gt;0,y&lt;0)</t>
+  </si>
+  <si>
+    <t>x;x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1;x</t>
+  </si>
+  <si>
+    <t>1;x+y@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>sin(x)+1;sin(x)@Or(sin(x)&gt;0,sin(x)&lt;0)</t>
+  </si>
+  <si>
+    <t>1;x@(x&gt;0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>x**2;y**2@Or(y&gt;0,y&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x**2@x&gt;=1;1/x@x&gt;=1</t>
+  </si>
+  <si>
+    <t>x**3*y**2;x*y@Or(x*y&gt;0,x*y&lt;0)</t>
+  </si>
+  <si>
+    <t>sin(2*x);cos(x)@Or(cos(x)&gt;0,cos(x)&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2+y**2;x+y@Or(x+y&gt;0,x+y&lt;0)</t>
+  </si>
+  <si>
+    <t>x**3+1;x+1@Or(x+1&gt;0,x+1&lt;0)</t>
+  </si>
+  <si>
+    <t>sqrt(x**2+y**2);1/sqrt(x**2+y**2)@Or(x**2+y**2&gt;0,x**2+y**2&lt;0)</t>
+  </si>
+  <si>
+    <t>x+sin(x);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**3;x**2@(x&gt;0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>x**4*y**3;x**2*y**2@Or(x*y&gt;0,x*y&lt;0)</t>
+  </si>
+  <si>
+    <t>x**5;x**3@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>exp(2*x);exp(x)</t>
+  </si>
+  <si>
+    <t>x*abs(x);x@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/x**3@x&gt;=1;1/x**2@x&gt;=1</t>
+  </si>
+  <si>
+    <t>取最大值（max(f(x),g(x))=h(x)或max(f(x,y),g(x,y))=h(x,y)）</t>
+  </si>
+  <si>
+    <t>abs(x);-abs(x)</t>
+  </si>
+  <si>
+    <t>abs(x)+abs(y);-abs(x)-abs(y)</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);sin(1/x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>sqrt(x**2+y**2);-sqrt(x**2+y**2)</t>
+  </si>
+  <si>
+    <t>sin(1/x)@Or(x&gt;0,x&lt;0);cos(1/x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>1/(x+y)@Or(x+y&gt;0,x+y&lt;0);1/(x-y)@Or(x-y&gt;0,x-y&lt;0)</t>
+  </si>
+  <si>
+    <t>x;exp(x)</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=D(x)（D 为狄利克雷函数）</t>
+  </si>
+  <si>
+    <t>abs(x)*y**2;x*abs(y)</t>
+  </si>
+  <si>
+    <t>x**2;x+1</t>
+  </si>
+  <si>
+    <t>x**3;x+1</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);1/x**2@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x;0</t>
+  </si>
+  <si>
+    <t>x;-x</t>
+  </si>
+  <si>
+    <t>x**2;y**2</t>
+  </si>
+  <si>
+    <t>x;2*x</t>
+  </si>
+  <si>
+    <t>x**2+y**2;0</t>
+  </si>
+  <si>
+    <t>x;2</t>
+  </si>
+  <si>
+    <t>x;0@(x&gt;=0)&amp;(x&lt;=1)</t>
+  </si>
+  <si>
+    <t>x**2;1</t>
+  </si>
+  <si>
+    <t>x**4;y**4</t>
+  </si>
+  <si>
+    <t>x**2;2*x**2</t>
+  </si>
+  <si>
+    <t>x**3*y;2*x**3*y</t>
+  </si>
+  <si>
+    <t>x**2+y**2;2*x**2+2*y**2</t>
+  </si>
+  <si>
+    <t>x*y;2*x*y</t>
+  </si>
+  <si>
+    <t>1;2</t>
+  </si>
+  <si>
+    <t>x**4*y**2;2*x**4*y**2</t>
+  </si>
+  <si>
+    <t>x**2;3*x**2</t>
+  </si>
+  <si>
+    <t>1/x**2@Or(x&gt;0,x&lt;0);1/x**3@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>取最小值（min(f(x),g(x))=h(x)或min(f(x,y),g(x,y))=h(x,y)）</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=1-D(x)</t>
+  </si>
+  <si>
+    <t>abs(x)+y;x+abs(y)</t>
+  </si>
+  <si>
+    <t>sign(x);1-sign(x)</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;F(x,y)=1/(x+y)+D(x,y),G(x,y)=1/(x-y)+1-D(x,y)</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;F(x,y)=|x|y+D(x,y),G(x,y)=x|y|+1-D(x,y)</t>
+  </si>
+  <si>
+    <t>abs(x)+x;abs(x)-x</t>
+  </si>
+  <si>
+    <t>x**2+1;-x**2+1</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;F(x)=1/x+D(x),G(x)=1/x²+1-D(x)</t>
+  </si>
+  <si>
+    <t>abs(x)+abs(y);x+y</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);x</t>
+  </si>
+  <si>
+    <t>sqrt(x**2+y**2);x+y</t>
+  </si>
+  <si>
+    <t>sin(1/x)@Or(x&gt;0,x&lt;0);x</t>
+  </si>
+  <si>
+    <t>1/(x+y)@Or(x+y&gt;0,x+y&lt;0);x+y</t>
+  </si>
+  <si>
+    <t>x;sin(x)</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=x</t>
+  </si>
+  <si>
+    <t>abs(x)*y**2;x**2*y</t>
+  </si>
+  <si>
+    <t>x**2+1;x**3</t>
+  </si>
+  <si>
+    <t>x**2;-x**2</t>
+  </si>
+  <si>
+    <t>x**2+y**2;-x**2-y**2</t>
+  </si>
+  <si>
+    <t>x**4+y**4;-x**4-y**4</t>
+  </si>
+  <si>
+    <t>x**3;-x**3</t>
+  </si>
+  <si>
+    <t>复合函数（f(g(x))=h(x)或h(f(x,y),g(x,y))=h(x,y)）</t>
+  </si>
+  <si>
+    <t>x**2;abs(x)</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;1;D(x)</t>
+  </si>
+  <si>
+    <t>0;sin(1/x)@Or(x&gt;0,x&lt;0)</t>
+  </si>
+  <si>
+    <t>x**2;x</t>
+  </si>
+  <si>
+    <t>1/x**2@Or(x&gt;0,x&lt;0);x</t>
+  </si>
+  <si>
+    <t>sqrt(abs(x));x</t>
+  </si>
+  <si>
+    <t>【无法转换】&gt;&gt;&gt;D(x);x</t>
+  </si>
+  <si>
+    <t>x**3;sin(x);sin(x)**3</t>
+  </si>
+  <si>
+    <t>sqrt(x**2+1);x**2;sqrt(x**4+1)</t>
+  </si>
+  <si>
+    <t>exp(x);y**2;exp(x)+y**2</t>
+  </si>
+  <si>
+    <t>x**2;cos(x);cos(x)**2</t>
+  </si>
+  <si>
+    <t>1/x@Or(x&gt;0,x&lt;0);x-1@(x&gt;1)&amp;(x&lt;2);1/(x-1)@Or(x-1&gt;0,x-1&lt;0)</t>
+  </si>
+  <si>
+    <t>sqrt(x)@x&gt;=0;y**2;sqrt(x)+y**2</t>
+  </si>
+  <si>
+    <t>ln(x)@x&gt;0;x**2@x&gt;0;2*ln(x)</t>
+  </si>
+  <si>
+    <t>x**3+1;x-1;(x-1)**3+1</t>
+  </si>
+  <si>
+    <t>x;x**2+y**2</t>
+  </si>
+  <si>
+    <t>x+y;x*y</t>
+  </si>
+  <si>
+    <t>x**2;sin(x)</t>
+  </si>
+  <si>
+    <t>x**4;x**2+y**2</t>
+  </si>
+  <si>
+    <t>x**3;x</t>
+  </si>
+  <si>
+    <t>x**2;x**2</t>
+  </si>
+  <si>
+    <t>exp(-x);x**2</t>
+  </si>
+  <si>
+    <t>x;x**3*y</t>
+  </si>
+  <si>
+    <t>abs(x);x**3</t>
+  </si>
+  <si>
+    <t>x+y;x**3*y</t>
+  </si>
+  <si>
+    <t>1;x**3</t>
+  </si>
+  <si>
+    <t>x**4;x**3*y**2</t>
+  </si>
+  <si>
+    <t>exp(-x);x**3</t>
+  </si>
+  <si>
+    <t>x**3;x**2+y**2</t>
+  </si>
+  <si>
+    <t>x+y;x**2+y**2</t>
+  </si>
   <si>
     <t>特例法大杀器-二元组合### ###（无需作答）</t>
   </si>
   <si>
-    <t>一阶或二阶可导（一元）+连续性（一元）</t>
-  </si>
-  <si>
     <t>00：Piecewise((1, x &gt;= 0), (-1, x &lt; 0))</t>
   </si>
   <si>
@@ -47,9 +1149,6 @@
     <t>11：x**2</t>
   </si>
   <si>
-    <t>一阶或二阶可导（一元）+极限存在（一元）</t>
-  </si>
-  <si>
     <t>00：Piecewise((sin(1/x), Ne(x, 0)), (0, Eq(x, 0)))</t>
   </si>
   <si>
@@ -59,18 +1158,12 @@
     <t>11：x**3</t>
   </si>
   <si>
-    <t>连续性（一元）+极限存在（一元）</t>
-  </si>
-  <si>
     <t>01：Piecewise((x, Ne(x, 0)), (1, Eq(x, 0)))</t>
   </si>
   <si>
     <t>11：x</t>
   </si>
   <si>
-    <t>偏导数存在（多元）+可微性（多元）</t>
-  </si>
-  <si>
     <t>00：abs(x) + abs(y)</t>
   </si>
   <si>
@@ -86,9 +1179,6 @@
     <t>特例法大杀器-三元组合### ###（无需作答）</t>
   </si>
   <si>
-    <t>一阶或二阶可导（一元）+连续性（一元）+极限存在（一元）</t>
-  </si>
-  <si>
     <t>000：Piecewise((1/x, Ne(x, 0)), (0, Eq(x, 0)))</t>
   </si>
   <si>
@@ -113,9 +1203,6 @@
     <t>111：x**2</t>
   </si>
   <si>
-    <t>偏导数存在（多元）+可微性（多元）+连续性（多元）</t>
-  </si>
-  <si>
     <t>000：Piecewise((1, Ne(x*y, 0)), (0, Eq(x*y, 0)))</t>
   </si>
   <si>
@@ -134,9 +1221,6 @@
     <t>111：x**2 + y**2</t>
   </si>
   <si>
-    <t>偏导数存在（多元）+可微性（多元）+二阶偏导连续（多元）</t>
-  </si>
-  <si>
     <t>000：abs(x) + abs(y)</t>
   </si>
   <si>
@@ -149,18 +1233,12 @@
     <t>111：x**3 + y**3</t>
   </si>
   <si>
-    <t>偏导数存在（多元）+连续性（多元）+二阶偏导连续（多元）</t>
-  </si>
-  <si>
     <t>000：Piecewise((1, x**2 + y**2 &gt;= 1), (0, x**2 + y**2 &lt; 1))</t>
   </si>
   <si>
     <t>010：abs(x) + abs(y)</t>
   </si>
   <si>
-    <t>可微性（多元）+连续性（多元）+二阶偏导连续（多元）</t>
-  </si>
-  <si>
     <t>110：Piecewise(((x**2*y**2)*sin(1/(x**2 + y**2)), Ne(x**2 + y**2, 0)), (0, And(Eq(x, 0), Eq(y, 0))))</t>
   </si>
   <si>
@@ -170,9 +1248,6 @@
     <t>性质排序参考20250616</t>
   </si>
   <si>
-    <t>相反数（-f(x)=g(x)或-f(x,y)=g(x,y)）</t>
-  </si>
-  <si>
     <t>00：###abs(x)###-###abs(x)+abs(y)###-###Piecewise((1,x&gt;=0),(-1,x&lt;0))###-###sqrt(abs(x*y))###-###Piecewise((sin(1/x),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###x+1###-###【无法转换】&gt;&gt;&gt;f(x)=分段函数{1,x为有理数；0,x为无理数}###-###(x**2*y)/(x**4 + y**2)###-###x**2+1###-###NA###-###NA###-###NA###-</t>
   </si>
   <si>
@@ -185,9 +1260,6 @@
     <t>11：###x**2###-###x**2 + y**2###-###x###-###x**2 + y**2###-###x###-###x + y###-###sin(x)###-###1###-###x**3 + y**3###-###x###-###x**2###-###x###-###1/x**2###-</t>
   </si>
   <si>
-    <t>绝对值（|f(x)|=g(x)或|f(x,y)|=g(x,y)）</t>
-  </si>
-  <si>
     <t>00：###abs(x)###-###abs(x)+abs(y)###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1,x≥0;-1,x&lt;0}###-###sqrt(abs(x*y))###-###Piecewise((sin(1/x),Ne(x,0)),(0,Eq(x,0)))###-###【无法转换】&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}###-###x+1###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数###-###(x**2*y)/(x**4 + y**2)###-###x###-###abs(x+1)###-###Piecewise((x,x&gt;=0),(2*x,x&lt;0))###-###1/x###-</t>
   </si>
   <si>
@@ -200,114 +1272,84 @@
     <t>11：###x**2###-###x**2+y**2###-###abs(x)###-###x**2+y**2###-###abs(x)###-###abs(x+y)###-###NA###-###1###-###x**4+y**4###-###0###-###x**2###-###x**2###-###exp(-x**2)###-</t>
   </si>
   <si>
-    <t>取倒数（1/f(x)=g(x)或1/f(x,y)=g(x,y)）</t>
-  </si>
-  <si>
-    <t>00：###&gt;&gt;&gt;f(x)=|x|（在x=0不可导）,g(x)=1/|x|（在x=0不可导，导数为无穷大）###-###&gt;&gt;&gt;f(x,y)=|x|+|y|（在(0,0)偏导数不存在）,g(x,y)=1/(|x|+|y|)（在(0,0)偏导数不存在）###-###&gt;&gt;&gt;f(x)=分段{1,x≥0;0,x&lt;0}（在x=0不连续）,g(x)=分段{1,x≥0;无定义，x&lt;0}（在x=0不连续且无定义）###-###&gt;&gt;&gt;f(x,y)=分段{x²+y²,(x,y)≠(0,0);0,(x,y)=(0,0)}（在(0,0)不可微）,g(x,y)=分段{1/(x²+y²),(x,y)≠(0,0);无定义，(x,y)=(0,0)}（在(0,0)不可微）###-###&gt;&gt;&gt;f(x)=分段{sin(1/x),x≠0;0,x=0}（x→0极限不存在）,g(x)=分段{1/sin(1/x),x≠0;无定义，x=0}（x→0极限不存在）###-###&gt;&gt;&gt;f(x,y)=分段{1,xy≠0;0,xy=0}（在(0,0)不连续）,g(x,y)=分段{1,xy≠0;无定义，xy=0}（在(0,0)不连续）###-###&gt;&gt;&gt;f(x)=x+1（非周期函数）,g(x)=1/(x+1)（非周期函数）###-###&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;无定义，x∉Q}（不可积）###-###&gt;&gt;&gt;f(x,y)=x²y/(x⁴+y²)（在(0,0)二阶偏导不连续）,g(x,y)=(x⁴+y²)/(x²y)（在(0,0)二阶偏导不连续）###-###&gt;&gt;&gt;f(x)=x²+1（非奇函数）,g(x)=1/(x²+1)（非奇函数）###-###&gt;&gt;&gt;f(x)=x+1（非偶函数）,g(x)=1/(x+1)（非偶函数）###-###&gt;&gt;&gt;f(x)=|x|（在x=0无切线）,g(x)=1/|x|（在x=0无定义，无切线）###-###&gt;&gt;&gt;f(x)=1/x（无穷积分∫1/xdx从1到∞发散）,g(x)=x（无穷积分∫xdx从1到∞发散）###-</t>
-  </si>
-  <si>
-    <t>01：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###exp(-x**2)###-###exp(x**2)###-</t>
-  </si>
-  <si>
-    <t>10：###x###-###1/x###-###x###-###1/x###-###NA###-###x**2+y**2+1###-###1/(x**2+y**2+1)###-###NA###-###NA###-###NA###-###x**2+y**2+1###-###1/(x**2+y**2+1)###-###NA###-###x+1###-###1/(x+1)###-###1/x**2###-###x**2###-</t>
+    <t>00：###abs(x);1/abs(x)###-###abs(x)+abs(y);1/(abs(x)+abs(y))###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0));Piecewise((1, x &gt;= 0), (nan, x &lt; 0))###-###Piecewise(((x**2 + y**2), Or(x &gt; 0, x &lt; 0) | Or(y &gt; 0, y &lt; 0)), (0, x == 0 &amp; y == 0));Piecewise((1/(x**2 + y**2), Or(x &gt; 0, x &lt; 0) | Or(y &gt; 0, y &lt; 0)), (nan, x == 0 &amp; y == 0))###-###Piecewise((sin(1/x), Or(x &gt; 0, x &lt; 0)), (0, x == 0));Piecewise((1/sin(1/x), Or(x &gt; 0, x &lt; 0)), (nan, x == 0))###-###Piecewise((1, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (0, x == 0 | y == 0));Piecewise((1, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (nan, x == 0 | y == 0))###-###x+1;1/(x+1)###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;无定义，x∉Q}（不可积）###-###(x**2*y)/(x**4+y**2);(x**4+y**2)/(x**2*y)###-###x**2+1;1/(x**2+1)###-###x+1;1/(x+1)###-###abs(x);1/abs(x)###-###1/x;x###-</t>
+  </si>
+  <si>
+    <t>01：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###exp(-x**2)###-</t>
+  </si>
+  <si>
+    <t>10：###x###-###x###-###NA###-###x**2+y**2+1###-###NA###-###NA###-###NA###-###NA###-###x**2+y**2+1###-###NA###-###NA###-###x+1###-###1/x**2@Or(x&gt;0,x&lt;0)###-</t>
   </si>
   <si>
     <t>11：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-</t>
   </si>
   <si>
-    <t>平方（f(x)²=g(x)或f(x,y)²=g(x,y)）</t>
-  </si>
-  <si>
-    <t>00：###Piecewise((x, Ne(x, 0)), (1, Eq(x, 0)))###-###Piecewise((x**2, Ne(x, 0)), (1, Eq(x, 0)))###-###abs(x)+abs(y)###-###(abs(x)+abs(y))**2###-###Piecewise((1, x&gt;=0), (0, x&lt;0))###-###Piecewise((1, x&gt;=0), (0, x&lt;0))###-###Piecewise((1, x&gt;=0), (0, x&lt;0))###-###Piecewise((1, x&gt;=0), (0, x&lt;0))###-###Piecewise((sin(1/x), Ne(x, 0)), (0, Eq(x, 0)))###-###Piecewise((sin(1/x)**2, Ne(x, 0)), (0, Eq(x, 0)))###-###Piecewise((1, Ne(x*y, 0)), (0, Eq(x*y, 0)))###-###Piecewise((1, Ne(x*y, 0)), (0, Eq(x*y, 0)))###-###x+1###-###(x+1)**2###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1,x为有理数；0,x为无理数}###-###【无法转换】&gt;&gt;&gt;g(x)=分段{1,x为有理数；0,x为无理数}###-###(x**2*y)/(x**4 + y**2)###-###((x**2*y)/(x**4 + y**2))**2###-###x+1###-###(x+1)**2###-###x+1###-###(x+1)**2###-###Piecewise((x, x&gt;=0), (2*x, x&lt;0))###-###Piecewise((x**2, x&gt;=0), (4*x**2, x&lt;0))###-###1/x###-###1/x**2###-</t>
-  </si>
-  <si>
-    <t>01：###NA###-###abs(x)###-###x**2###-###NA###-###abs(x)###-###x**2###-###Piecewise((1, x&gt;0), (-1, x&lt;0), (0, Eq(x, 0)))###-###Piecewise((1, Ne(x, 0)), (0, Eq(x, 0)))###-###Piecewise((2, Ne(x*y, 0)), (0, Eq(x*y, 0)))###-###4###-###abs(sin(x))###-###sin(x)**2###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1,x∈Q;-1,x∉Q}###-###1###-###NA###-###NA###-###x###-###x**2###-###abs(x)###-###x**2###-###1/x###-###1/x**2###-</t>
-  </si>
-  <si>
-    <t>10：###x###-###x**2###-###x###-###x**2###-###NA###-###x###-###x**2###-###NA###-###NA###-###NA###-###x**3###-###x**6###-###x###-###x**2###-###x**2###-###x**4###-###x###-###x**2###-###1/x**2###-###1/x**4###-</t>
-  </si>
-  <si>
-    <t>11：###x**2###-###x**4###-###x**2+y**2###-###(x**2+y**2)**2###-###x###-###x**2###-###x###-###x**2###-###x###-###x**2###-###x+y###-###(x+y)**2###-###sin(x)###-###sin(x)**2###-###1###-###1###-###x**4+y**4###-###(x**4+y**4)**2###-###x###-###x**2###-###x**2###-###x**4###-###x###-###x**2###-###exp(-x)###-###exp(-2*x)###-</t>
-  </si>
-  <si>
-    <t>立方（f(x)³=g(x)或f(x,y)³=g(x,y)）</t>
-  </si>
-  <si>
-    <t>00：###abs(x)###-###abs(x)**3###-###abs(x)+abs(y)###-###(abs(x)+abs(y))**3###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((sin(1/x),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((sin(1/x)**3,Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###x+1###-###(x+1)**3###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数###-###【无法转换】&gt;&gt;&gt;g(x)=分段{1,x∈Q;0,x∉Q}###-###(x**2*y)/(x**4 + y**2)###-###((x**2*y)/(x**4 + y**2))**3###-###x+1###-###(x+1)**3###-###x+1###-###(x+1)**3###-###Piecewise((x,x&gt;=0),(2*x,x&lt;0))###-###Piecewise((x**3,x&gt;=0),(8*x**3,x&lt;0))###-###1/x###-###1/x**3###-</t>
-  </si>
-  <si>
-    <t>01：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###1/x###-###1/x**3###-</t>
-  </si>
-  <si>
-    <t>10：###x###-###x**3###-###x###-###x**3###-###NA###-###x###-###x**3###-###NA###-###NA###-###NA###-###x**3###-###x**9###-###x###-###x**3###-###x**2###-###x**6###-###x###-###x**3###-###1/x**2###-###1/x**6###-</t>
-  </si>
-  <si>
-    <t>11：###x**2###-###x**6###-###x**2+y**2###-###(x**2+y**2)**3###-###x###-###x**3###-###x###-###x**3###-###x###-###x**3###-###x+y###-###(x+y)**3###-###NA###-###1###-###1###-###x**4+y**4###-###(x**4+y**4)**3###-###x###-###x**3###-###x**2###-###x**6###-###x###-###x**3###-###exp(-x)###-###exp(-3*x)###-</t>
-  </si>
-  <si>
-    <t>平方根（sqrt(f(x))=g(x)或sqrt(f(x,y))=g(x,y)）</t>
-  </si>
-  <si>
-    <t>00：###abs(x)###-###sqrt(abs(x))###-###abs(x)+abs(y)###-###sqrt(abs(x)+abs(y))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((sin(1/x)**2,Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((abs(sin(1/x)),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###x**2+1###-###sqrt(x**2+1)###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数###-###【无法转换】&gt;&gt;&gt;g(x)=分段{1,x∈Q;0,x∉Q}###-###(x**2*y**2)/(x**4+y**4)###-###(abs(x*y))/sqrt(x**4+y**4)###-###x**2###-###abs(x)###-###x**2+1###-###sqrt(x**2+1)###-###Piecewise((x**2,x&gt;=0),(2*x**2,x&lt;0))###-###Piecewise((abs(x),x&gt;=0),(abs(x)*sqrt(2),x&lt;0))###-###1/x**4###-###1/x**2###-</t>
-  </si>
-  <si>
-    <t>01：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###1/x**4###-###1/x**2###-</t>
-  </si>
-  <si>
-    <t>10：###x**2###-###abs(x)###-###x**2+y**2###-###sqrt(x**2+y**2)###-###NA###-###x**2+y**2###-###sqrt(x**2+y**2)###-###NA###-###NA###-###NA###-###x**4+y**4###-###sqrt(x**4+y**4)###-###x**2###-###abs(x)###-###x**2###-###abs(x)###-###x**2###-###abs(x)###-###1/x**4###-###1/x**2###-</t>
-  </si>
-  <si>
-    <t>立方根（curt(f(x))=g(x)或curt(f(x,y))=g(x,y)）</t>
-  </si>
-  <si>
-    <t>00：###abs(x)###-###x**(1/3)###-###abs(x)+abs(y)###-###(abs(x)+abs(y))**(1/3)###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((sin(1/x),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise(((sin(1/x))**(1/3),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###x+1###-###(x+1)**(1/3)###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数###-###【无法转换】&gt;&gt;&gt;g(x)=分段{1,x∈Q;0,x∉Q}###-###(x**2*y)/(x**4 + y**2)###-###((x**2*y)/(x**4 + y**2))**(1/3)###-###x**2+1###-###(x**2+1)**(1/3)###-###x+1###-###(x+1)**(1/3)###-###abs(x)###-###(abs(x))**(1/3)###-###1/x###-###1/(x**(1/3))###-</t>
-  </si>
-  <si>
-    <t>01：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###1/x**3###-###1/x###-</t>
-  </si>
-  <si>
-    <t>10：###x**2###-###(x**2)**(1/3)###-###x**2+y**2###-###(x**2+y**2)**(1/3)###-###NA###-###x**3###-###x###-###NA###-###NA###-###NA###-###x**6+y**6###-###x**2+y**2###-###x**3###-###x###-###x**6###-###x**2###-###x**3###-###x###-###1/x**6###-###1/x**2###-</t>
-  </si>
-  <si>
-    <t>11：###x**3###-###x###-###x**3+y**3###-###x+y###-###x###-###x**(1/3)###-###x**3+y**3###-###x+y###-###x###-###x**(1/3)###-###x+y###-###(x+y)**(1/3)###-###sin(x)###-###(sin(x))**(1/3)###-###1###-###1###-###x**6+y**6###-###x**2+y**2###-###x**3###-###x###-###x**6###-###x**2###-###x**3###-###x###-###exp(-3*x)###-###exp(-x)###-</t>
-  </si>
-  <si>
-    <t>向上取整（ceil(f(x))=g(x)或ceil(f(x,y))=g(x,y)）</t>
-  </si>
-  <si>
-    <t>00：###abs(x)###-###ceiling(abs(x))###-###abs(x)+abs(y)###-###ceiling(abs(x)+abs(y))###-###Piecewise((0.5,x&gt;=0),(-0.5,x&lt;0))###-###Piecewise((1,x&gt;=0),(0,x&lt;0))###-###Piecewise((0.5,xy&lt;0),(1.5,xy&gt;=0))###-###Piecewise((1,xy&lt;0),(2,xy&gt;=0))###-###Piecewise((sin(1/x),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((ceiling(sin(1/x)),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((1-|x*y|,Ne(x*y,0)),(0,Eq(x*y,0)))###-###Piecewise((1,Ne(x*y,0)),(0,Eq(x*y,0)))###-###x+sin(x)###-###ceiling(x+sin(x))###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1.5,x∈Q;1,x∉Q}###-###【无法转换】&gt;&gt;&gt;g(x)=分段{2,x∈Q;1,x∉Q}###-###(x**2*y)/(x**4 + y**2)+1###-###ceiling((x**2*y)/(x**4 + y**2)+1)###-###x###-###ceiling(x)###-###x**2###-###ceiling(x**2)###-###x###-###ceiling(x)###-###1/x###-###ceiling(1/x)###-</t>
-  </si>
-  <si>
-    <t>01：###abs(x)###-###ceiling(abs(x)+0.5)###-###abs(x)###-###ceiling(abs(x)+0.5)###-###Piecewise((2.2,x&lt;0),(2.8,x&gt;=0))###-###2###-###abs(x)###-###ceiling(abs(x)+0.5)###-###Piecewise((0.5,x&lt;0),(1.5,x&gt;=0))###-###Piecewise((1,x&lt;0),(2,x&gt;=0))###-###Piecewise((0.5,xy&lt;0),(1.5,xy&gt;=0))###-###Piecewise((1,xy&lt;0),(2,xy&gt;=0))###-###abs(0.5*sin(x))+0.5###-###1###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数###-###1###-###(x**2*y**2)/(x**4+y**4)###-###0###-###x+1###-###ceiling(x+1)###-###x+1###-###ceiling(x+1)###-###abs(x)###-###ceiling(abs(x)+0.5)###-###1/x+1###-###2###-</t>
-  </si>
-  <si>
-    <t>10：###x###-###ceiling(x)###-###x###-###ceiling(x)###-###x###-###ceiling(x)###-###x###-###ceiling(x)###-###x###-###ceiling(x)###-###x+y###-###ceiling(x+y)###-###x###-###ceiling(x)###-###x###-###ceiling(x)###-###x**3###-###ceiling(x**3)###-###x###-###ceiling(x)###-###x**2###-###ceiling(x**2)###-###x###-###ceiling(x)###-###exp(-x)###-###1###-</t>
-  </si>
-  <si>
-    <t>11：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###sin(x)###-###ceiling(sin(x))###-###x+0.5###-###1###-###x**3###-###ceiling(x**3)###-###NA###-###x**2###-###ceiling(x**2)###-###NA###-###NA###-</t>
-  </si>
-  <si>
-    <t>向下取整（floor(f(x))=g(x)或floor(f(x,y))=g(x,y)）</t>
-  </si>
-  <si>
-    <t>00：###abs(x)###-###floor(abs(x))###-###abs(x)+abs(y)###-###floor(abs(x)+abs(y))###-###Piecewise((0.5,x&lt;0),(1.5,x&gt;=0))###-###Piecewise((0,x&lt;0),(1,x&gt;=0))###-###Piecewise((0.5,xy&lt;0),(1.5,xy&gt;=0))###-###Piecewise((0,xy&lt;0),(1,xy&gt;=0))###-###Piecewise((sin(1/x),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((floor(sin(1/x)),Ne(x,0)),(0,Eq(x,0)))###-###Piecewise((1-|x*y|,Ne(x*y,0)),(0,Eq(x*y,0)))###-###0###-###x+sin(x)###-###floor(x+sin(x))###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1.5,x∈Q;1,x∉Q}###-###1###-###(x**2*y)/(x**4 + y**2)###-###0###-###x+1###-###floor(x+1)###-###x+1###-###floor(x+1)###-###abs(x)###-###floor(abs(x))###-###NA###-</t>
-  </si>
-  <si>
-    <t>01：###abs(x)+0.5###-###1###-###abs(x)+0.5###-###1###-###Piecewise((2.2,x&lt;0),(2.8,x&gt;=0))###-###2###-###abs(x)+0.5###-###1###-###NA###-###Piecewise((0.5,xy&lt;0),(0.25,xy&gt;=0))###-###0###-###NA###-###abs(0.5*sin(x))+0.5###-###1###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数###-###1###-###(x**2*y)/(x**4 + y**2)###-###0###-###Piecewise((1.5,x&gt;0),(0.5,x=0),(-0.5,x&lt;0))###-###Piecewise((1,x&gt;0),(0,x=0),(-1,x&lt;0))###-###Piecewise((0,x≠1),(0.5,x=1))###-###0###-###abs(x)+0.5###-###0###-###1/x+1###-###1###-</t>
-  </si>
-  <si>
-    <t>10：###x###-###floor(x)###-###x###-###floor(x)###-###NA###-###x###-###floor(x)###-###x###-###floor(x)###-###NA###-###NA###-###x###-###floor(x)###-###x+y###-###floor(x+y)###-###NA###-###NA###-###x**3###-###floor(x**3)###-###NA###-###x**2###-###floor(x**2)###-###x###-###floor(x)###-###NA###-</t>
-  </si>
-  <si>
-    <t>11：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###sin(x)###-###floor(sin(x))###-###x+0.5###-###0###-###NA###-###NA###-###x**2###-###floor(x**2)###-###x+0.5###-###0###-###exp(-x)###-###0###-</t>
+    <t>00：###Piecewise((x, Or(x&gt;0,x&lt;0)), (1, x==0))###-###abs(x)+abs(y)###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((sin(1/x), Or(x&gt;0,x&lt;0)), (0, x==0))###-###Piecewise((1, Or(x&gt;0,x&lt;0) &amp; Or(y&gt;0,y&lt;0)), (0, x==0 | y==0))###-###x+1###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）###-###(x**2*y)/(x**4+y**2)###-###x+1###-###x+1###-###Piecewise((x, x &gt;= 0), (2*x, x &lt; 0))###-###1/x@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>01：###NA###-###abs(x)###-###NA###-###abs(x)###-###Piecewise((1, x&gt;0), (-1, x&lt;0), (0, x==0))###-###Piecewise((2, Or(x&gt;0,x&lt;0) &amp; Or(y&gt;0,y&lt;0)), (0, x==0 | y==0))###-###abs(sin(x))###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1,x∈Q;-1,x∉Q}（不可积）###-###NA###-###NA###-###x###-###abs(x)###-###1/x@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>10：###x###-###x###-###NA###-###x###-###NA###-###NA###-###NA###-###NA###-###x**3###-###x###-###x**2###-###x###-###1/x**2@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>11：###x**2###-###x**2+y**2###-###x###-###x###-###x###-###x+y###-###sin(x)###-###1###-###x**4+y**4###-###x###-###x**2###-###x###-###exp(-x)###-</t>
+  </si>
+  <si>
+    <t>00：###abs(x)###-###abs(x)+abs(y)###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((sin(1/x), Or(x &gt; 0, x &lt; 0)), (0, x == 0))###-###Piecewise((1, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (0, x == 0 | y == 0))###-###x+1###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）###-###(x**2*y)/(x**4+y**2)###-###x+1###-###Piecewise((x, x &gt;= 0), (2*x, x &lt; 0))###-###1/x@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>01：###NA###-###abs(x)###-###NA###-###abs(x)###-###Piecewise((1, x &gt; 0), (-1, x &lt; 0), (0, x == 0))###-###Piecewise((2, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (0, x == 0 | y == 0))###-###abs(sin(x))###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1,x∈Q;-1,x∉Q}（不可积）###-###NA###-###NA###-###x###-###abs(x)###-###1/x@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>00：###abs(x);sqrt(abs(x))###-###abs(x)+abs(y);sqrt(abs(x)+abs(y))###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0));Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0));Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((sin(1/x)**2, Or(x &gt; 0, x &lt; 0)), (0, x == 0));Piecewise((abs(sin(1/x)), Or(x &gt; 0, x &lt; 0)), (0, x == 0))###-###Piecewise((1, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (0, x == 0 | y == 0));Piecewise((1, Or(x &gt; 0, x &lt; 0) &amp; Or(y &gt; 0, y &lt; 0)), (0, x == 0 | y == 0))###-###x**2+1;sqrt(x**2+1)###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）;分段{1,x∈Q;0,x∉Q}（不可积）###-###(x**2*y**2)/(x**4+y**4);(abs(x*y))/sqrt(x**4+y**4)###-###x**2;abs(x)###-###x**2+1;sqrt(x**2+1)###-###Piecewise((x**2, x &gt;= 0), (2*x**2, x &lt; 0));Piecewise((abs(x), x &gt;= 0), (abs(x)*sqrt(2), x &lt; 0))###-###1/x**4@Or(x&gt;0,x&lt;0);1/x**2@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>01：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###1/x**4@Or(x&gt;0,x&lt;0);1/x**2@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>10：###x**2;abs(x)###-###x**2+y**2;sqrt(x**2+y**2)###-###NA###-###x**2+y**2;sqrt(x**2+y**2)###-###NA###-###NA###-###NA###-###NA###-###x**4+y**4;sqrt(x**4+y**4)###-###x**2;abs(x)###-###x**2;abs(x)###-###x**2;abs(x)###-###1/x**4@Or(x&gt;0,x&lt;0);1/x**2@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>00：###abs(x);abs(x)**(1/3)###-###abs(x)+abs(y);(abs(x)+abs(y))**(1/3)###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0));Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0));Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((sin(1/x), Or(x &gt; 0, x &lt; 0)), (0, x == 0));Piecewise((sin(1/x)**(1/3), Or(x &gt; 0, x &lt; 0)), (0, x == 0))###-###Piecewise((1, (Or(x &gt; 0, x &lt; 0)) &amp; (Or(y &gt; 0, y &lt; 0))), (0, x == 0 | y == 0));Piecewise((1, (Or(x &gt; 0, x &lt; 0)) &amp; (Or(y &gt; 0, y &lt; 0))), (0, x == 0 | y == 0))###-###x+1;(x+1)**(1/3)###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）,g(x)=分段{1,x∈Q;0,x∉Q}（不可积）###-###(x**2*y)/(x**4+y**2);((x**2*y)/(x**4+y**2))**(1/3)###-###x**2+1;(x**2+1)**(1/3)###-###x+1;(x+1)**(1/3)###-###abs(x);abs(x)**(1/3)###-###1/x@Or(x&gt;0,x&lt;0);1/x**(1/3)@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>01：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###1/x**3@Or(x&gt;0,x&lt;0);1/x@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>10：###x**2;(x**2)**(1/3)###-###x**2+y**2;(x**2+y**2)**(1/3)###-###NA###-###x**3;x###-###NA###-###NA###-###NA###-###NA###-###x**6+y**6;x**2+y**2###-###x**3;x###-###x**6;x**2###-###x**3;x###-###1/x**6@Or(x&gt;0,x&lt;0);1/x**2@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>11：###x**3;x###-###x**3+y**3;x+y###-###x;x**(1/3)###-###x**3+y**3;x+y###-###x;x**(1/3)###-###x+y;(x+y)**(1/3)###-###sin(x);sin(x)**(1/3)###-###1;1###-###x**6+y**6;x**2+y**2###-###x**3;x###-###x**6;x**2###-###x**3;x###-###exp(-3x);exp(-x)###-</t>
+  </si>
+  <si>
+    <t>00：###abs(x)###-###abs(x)+abs(y)###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((1, x &gt;= 0), (0, x &lt; 0))###-###Piecewise((sin(1/x), Or(x &gt; 0, x &lt; 0)), (0, x == 0))###-###Piecewise((1 - abs(x*y), (x*y &gt; 0) | (x*y &lt; 0)), (0, x == 0 &amp; y == 0))###-###x + sin(x)###-###【无法转换】&gt;&gt;&gt;f(x)=分段{1.5,x∈Q;1,x∉Q}（不可积，不满足性质H）###-###(x**2*y)/(x**4+y**2)+1###-###x###-###x**2###-###x###-###1/x@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>01：###abs(x)###-###abs(x)###-###Piecewise((2.2, x &lt; 0), (2.8, x &gt;= 0))###-###abs(x)###-###Piecewise((0.5, x &lt; 0), (1.5, x &gt;= 0))###-###Piecewise((0.5, x*y &lt; 0), (1.5, x*y &gt;= 0))###-###abs(0.5*sin(x))+0.5###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）###-###(x**2*y**2)/(x**4+y**4)###-###x+1###-###x+1###-###abs(x)###-###1/x+1@Or(x&gt;0,x&lt;0)###-</t>
+  </si>
+  <si>
+    <t>10：###x###-###x###-###NA###-###x###-###NA###-###NA###-###NA###-###NA###-###x**3###-###x###-###x**2###-###x###-###exp(-x)###-</t>
+  </si>
+  <si>
+    <t>11：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###sin(x)###-###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-</t>
+  </si>
+  <si>
+    <t>00：###abs(x);floor(abs(x))###-###abs(x)+abs(y);floor(abs(x)+abs(y))###-###Piecewise((0.5, x &lt; 0), (1.5, x &gt;= 0));Piecewise((0, x &lt; 0), (1, x &gt;= 0))###-###Piecewise((0.5, x*y &lt; 0), (1.5, x*y &gt;= 0));Piecewise((0, x*y &lt; 0), (1, x*y &gt;= 0))###-###Piecewise((sin(1/x), Or(x &gt; 0, x &lt; 0)), (0, x == 0));Piecewise((floor(sin(1/x)), Or(x &gt; 0, x &lt; 0)), (0, x == 0))###-###Piecewise((1 - abs(x*y), Or(x*y &gt; 0, x*y &lt; 0)), (0, x*y == 0));0###-###x + sin(x);floor(x + sin(x))###-###【无法转换】&gt;&gt;&gt;分段{1.5,x∈Q;1,x∉Q};1###-###(x**2*y)/(x**4+y**2);0###-###x+1;floor(x+1)###-###x+1;floor(x+1)###-###abs(x);floor(abs(x))###-###NA###-</t>
+  </si>
+  <si>
+    <t>01：###abs(x)+0.5;1###-###abs(x)+0.5;1###-###Piecewise((2.2, x &lt; 0), (2.8, x &gt;= 0));2###-###abs(x)+0.5;0###-###NA###-###Piecewise((0.5, x*y &lt; 0), (0.25, x*y &gt;= 0));0###-###NA###-###【无法转换】&gt;&gt;&gt;f(x)=狄利克雷函数（不可积）;1###-###(x**2*y)/(x**4+y**2);0###-###Piecewise((1.5, x &gt; 0), (0.5, x == 0), (-0.5, x &lt; 0));Piecewise((1, x &gt; 0), (0, x == 0), (-1, x &lt; 0))###-###Piecewise((0, Or(x &gt; 1, x &lt; 1)), (0.5, x == 1));0###-###abs(x)+0.5;0###-###1/x+1@Or(x&gt;0,x&lt;0);1###-</t>
+  </si>
+  <si>
+    <t>10：###x;floor(x)###-###x;floor(x)###-###NA###-###x;floor(x)###-###NA###-###NA###-###NA###-###NA###-###x**3;floor(x**3)###-###NA###-###x**2;floor(x**2)###-###x;floor(x)###-###NA###-</t>
+  </si>
+  <si>
+    <t>11：###NA###-###NA###-###NA###-###NA###-###NA###-###NA###-###sin(x);floor(sin(x))###-###x+0.5;0###-###NA###-###NA###-###x**2;floor(x**2)###-###x+0.5;0###-###exp(-x);0###-</t>
   </si>
   <si>
     <t>特例法大杀器-二元运算### ###（无需作答）</t>
   </si>
   <si>
-    <t>加减（f(x)±g(x)=h(x)或f(x,y)±g(x,y)=h(x,y)）</t>
-  </si>
-  <si>
     <t>000：###abs(x);abs(x)###-###abs(x)+abs(y);abs(x)+abs(y)###-###1/x;1/x@Or(x&gt;0,x&lt;0)###-###1/sqrt(x**2+y**2);1/sqrt(x**2+y**2)###-###1/x;1/x@Or(x&gt;0,x&lt;0)###-###1/(x+y);1/(x+y)@Or(x+y&gt;0,x+y&lt;0)###-###sin(x)+1/x;cos(x)+1/x@Or(x&gt;0,x&lt;0)###-###1/x;x@(x&gt;=0)&amp;(x&lt;=1)###-###1/(x+y);y@Or(x+y&gt;0,x+y&lt;0)###-###x**2+1;x**2+1###-###x+1;x+1###-###abs(x);abs(x)###-###1/x;1/x**2@x&gt;=1###-</t>
   </si>
   <si>
@@ -326,9 +1368,6 @@
     <t>111：###x;x**2###-###x*y;x**2*y###-###x;x**2###-###x*y;x**2*y###-###x;x**2###-###x*y;x**2*y###-###sin(x);sin(x)###-###x;x**2@(x&gt;=0)&amp;(x&lt;=1)###-###x*y;x**2*y###-###x;x**3###-###x**2;x**4###-###x;x**2###-###1/x**2;1/x**3@x&gt;=1###-</t>
   </si>
   <si>
-    <t>乘法（f(x)*g(x)=h(x)或f(x,y)*g(x,y)=h(x,y)）</t>
-  </si>
-  <si>
     <t>000：###abs(x)+1;abs(x)+1###-###1/sqrt(x**2+y**2);1/sqrt(x**2+y**2)###-###1/x@Or(x&gt;0,x&lt;0);1/x@Or(x&gt;0,x&lt;0)###-###1/sqrt(x**2+y**2);1/sqrt(x**2+y**2)###-###1/x@Or(x&gt;0,x&lt;0);1/x@Or(x&gt;0,x&lt;0)###-###1/(x+y)@Or(x+y&gt;0,x+y&lt;0);1/(x+y)@Or(x+y&gt;0,x+y&lt;0)###-###sin(x)+1/x@Or(x&gt;0,x&lt;0);cos(x)+1/x@Or(x&gt;0,x&lt;0)###-###1/x@Or(x&gt;0,x&lt;0);1/x@(x&gt;=0)&amp;(x&lt;=1)###-###1/(x+y)@Or(x+y&gt;0,x+y&lt;0);1/(x+y)@Or(x+y&gt;0,x+y&lt;0)###-###x**2+1;x**2+1###-###x+1;x+1###-###abs(x);abs(x)###-###1/sqrt(x)@x&gt;=1;1/sqrt(x)@x&gt;=1###-</t>
   </si>
   <si>
@@ -347,9 +1386,6 @@
     <t>111：###x;x**2###-###x*y;x**2*y###-###x;x**2###-###x*y;x**2*y###-###x;x**2###-###x*y;x**2*y###-###sin(x);sin(x)###-###x;x**2@(x&gt;=0)&amp;(x&lt;=1)###-###x*y;x**2*y###-###x;x**3###-###x**2;x**4###-###x;x**2###-###1/x**2@x&gt;=1;1/x**3@x&gt;=1###-</t>
   </si>
   <si>
-    <t>除法（f(x)/g(x)=h(x)或f(x,y)/g(x,y)=h(x,y)）</t>
-  </si>
-  <si>
     <t>000：###x**2;x@Or(x&gt;0,x&lt;0)###-###x**2*y;x*y@Or(x*y&gt;0,x*y&lt;0)###-###x+1;1###-###x**2+y**2;1###-###x**3;x@Or(x&gt;0,x&lt;0)###-###x+y;2###-###sin(2*x);sin(x)@Or(sin(x)&gt;0,sin(x)&lt;0)###-###1;2@(x&gt;=0)&amp;(x&lt;=1)###-###x**3*y**3;x*y@Or(x*y&gt;0,x*y&lt;0)###-###x**2;x**4###-###x+1;1###-###x;1###-###1/x**2;1@x&gt;=1###-</t>
   </si>
   <si>
@@ -374,9 +1410,6 @@
     <t>111：###x**4;x**2@Or(x&gt;0,x&lt;0)###-###x**3*y**2;x*y@Or(x*y&gt;0,x*y&lt;0)###-###sin(2*x);cos(x)@Or(cos(x)&gt;0,cos(x)&lt;0)###-###x**2+y**2;x+y@Or(x+y&gt;0,x+y&lt;0)###-###x**3+1;x+1@Or(x+1&gt;0,x+1&lt;0)###-###sqrt(x**2+y**2);1/sqrt(x**2+y**2)@Or(x**2+y**2&gt;0,x**2+y**2&lt;0)###-###x+sin(x);x@Or(x&gt;0,x&lt;0)###-###x**3;x**2@(x&gt;0)&amp;(x&lt;=1)###-###x**4*y**3;x**2*y**2@Or(x*y&gt;0,x*y&lt;0)###-###x**5;x**3@Or(x&gt;0,x&lt;0)###-###exp(2*x);exp(x)###-###x*abs(x);x@Or(x&gt;0,x&lt;0)###-###1/x**3@x&gt;=1;1/x**2@x&gt;=1###-</t>
   </si>
   <si>
-    <t>取最大值（max(f(x),g(x))=h(x)或max(f(x,y),g(x,y))=h(x,y)）</t>
-  </si>
-  <si>
     <t>000：###abs(x);-abs(x)###-###abs(x)+abs(y);-abs(x)-abs(y)###-###1/x@Or(x&gt;0,x&lt;0);sin(1/x)@Or(x&gt;0,x&lt;0)###-###sqrt(x**2+y**2);-sqrt(x**2+y**2)###-###sin(1/x)@Or(x&gt;0,x&lt;0);cos(1/x)@Or(x&gt;0,x&lt;0)###-###1/(x+y)@Or(x+y&gt;0,x+y&lt;0);1/(x-y)@Or(x-y&gt;0,x-y&lt;0)###-###x;exp(x)###-###【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=D(x)（D 为狄利克雷函数）###-###abs(x)*y**2;x*abs(y)###-###x**2;x+1###-###x**3;x+1###-###abs(x);-abs(x)###-###1/x@Or(x&gt;0,x&lt;0);1/x**2@Or(x&gt;0,x&lt;0)###-</t>
   </si>
   <si>
@@ -395,9 +1428,6 @@
     <t>111：###x**2;2*x**2###-###x**3*y;2*x**3*y###-###sin(x);cos(x)###-###x**2+y**2;2*x**2+2*y**2###-###x;2*x###-###x*y;2*x*y###-###sin(x);sin(2*x)###-###1;2###-###x**4*y**2;2*x**4*y**2###-###x;2*x###-###x**2;2*x**2###-###x**2;3*x**2###-###1/x**2@Or(x&gt;0,x&lt;0);1/x**3@Or(x&gt;0,x&lt;0)###-</t>
   </si>
   <si>
-    <t>取最小值（min(f(x),g(x))=h(x)或min(f(x,y),g(x,y))=h(x,y)）</t>
-  </si>
-  <si>
     <t>001：###【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=1-D(x)###-###abs(x)+y;x+abs(y)###-###【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=1-D(x)###-###abs(x)+y;x+abs(y)###-###sign(x);1-sign(x)###-###【无法转换】&gt;&gt;&gt;F(x,y)=1/(x+y)+D(x,y),G(x,y)=1/(x-y)+1-D(x,y)###-###【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=1-D(x)###-###【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=1-D(x)###-###【无法转换】&gt;&gt;&gt;F(x,y)=|x|y+D(x,y),G(x,y)=x|y|+1-D(x,y)###-###abs(x)+x;abs(x)-x###-###x**2+1;-x**2+1###-###【无法转换】&gt;&gt;&gt;F(x)=D(x),G(x)=1-D(x)###-###【无法转换】&gt;&gt;&gt;F(x)=1/x+D(x),G(x)=1/x²+1-D(x)###-</t>
   </si>
   <si>
@@ -408,9 +1438,6 @@
   </si>
   <si>
     <t>111：###x**2;3*x**2###-###x**3*y;2*x**3*y###-###sin(x);cos(x)###-###x**2+y**2;2*x**2+2*y**2###-###x;2*x###-###x*y;2*x*y###-###sin(x);sin(2*x)###-###1;2###-###x**4*y**2;2*x**4*y**2###-###x;2*x###-###x**2;2*x**2###-###x**2;3*x**2###-###1/x**2@Or(x&gt;0,x&lt;0);1/x**3@Or(x&gt;0,x&lt;0)###-</t>
-  </si>
-  <si>
-    <t>复合函数（f(g(x))=h(x)或h(f(x,y),g(x,y))=h(x,y)）</t>
   </si>
   <si>
     <t>000：###x**2;3*x**2###-###x**3*y;2*x**3*y###-###sin(x);cos(x)###-###x**2+y**2;2*x**2+2*y**2###-###x;2*x###-###x*y;2*x*y###-###sin(x);sin(2*x)###-###1;2###-###x**4*y**2;2*x**4*y**2###-###x;2*x###-###x**2;2*x**2###-###x**2;3*x**2###-###1/x**2@Or(x&gt;0,x&lt;0);1/x**3@Or(x&gt;0,x&lt;0)###-</t>
@@ -1050,9 +2077,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1372,12 +2405,6821 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="5" width="50.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="50.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AB45"/>
+  <sheetFormatPr defaultColWidth="50.7777777777778" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="5" max="5" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="7" max="7" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="8" max="8" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="9" max="9" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="11" max="11" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="13" max="13" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="15" max="15" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="16" max="16" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="17" max="17" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="19" max="19" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="20" max="20" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="21" max="21" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="22" max="22" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="23" max="23" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="24" max="24" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="25" max="25" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="26" max="26" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="27" max="27" width="50.7777777777778" style="2" customWidth="1"/>
+    <col min="28" max="28" width="5.77777777777778" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="50.7777777777778" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="3:27">
+      <c r="C1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:28">
+      <c r="A2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="2:28">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:28">
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:28">
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:28">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:28">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W8" s="2">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:28">
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:28">
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:28">
+      <c r="A12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:28">
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:28">
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:28">
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:28">
+      <c r="A17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:28">
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:28">
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:28">
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB20" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:26">
+      <c r="A22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:28">
+      <c r="B23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:28">
+      <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:28">
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB25" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:28">
+      <c r="A27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB27" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:28">
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB28" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="2:28">
+      <c r="B29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB29" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="2:28">
+      <c r="B30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:28">
+      <c r="A32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB32" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="2:28">
+      <c r="B33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB33" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="2:28">
+      <c r="B34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB34" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="2:28">
+      <c r="B35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB35" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:28">
+      <c r="A37" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB37" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="2:28">
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="2:28">
+      <c r="B39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA39" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB39" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="2:28">
+      <c r="B40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB40" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:28">
+      <c r="A42" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB42" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="2:28">
+      <c r="B43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="X43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y43" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA43" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB43" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:28">
+      <c r="B44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB44" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:28">
+      <c r="B45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y45" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA45" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB45" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AB46"/>
+  <sheetFormatPr defaultColWidth="5.77777777777778" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.77777777777778" customWidth="1"/>
+    <col min="3" max="3" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77777777777778" customWidth="1"/>
+    <col min="5" max="5" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77777777777778" customWidth="1"/>
+    <col min="7" max="7" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77777777777778" customWidth="1"/>
+    <col min="9" max="9" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77777777777778" customWidth="1"/>
+    <col min="11" max="11" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.77777777777778" customWidth="1"/>
+    <col min="13" max="13" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77777777777778" customWidth="1"/>
+    <col min="15" max="15" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77777777777778" customWidth="1"/>
+    <col min="17" max="17" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.77777777777778" customWidth="1"/>
+    <col min="19" max="19" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.77777777777778" customWidth="1"/>
+    <col min="21" max="21" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="22" max="22" width="5.77777777777778" customWidth="1"/>
+    <col min="23" max="23" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="24" max="24" width="5.77777777777778" customWidth="1"/>
+    <col min="25" max="25" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="26" max="26" width="5.77777777777778" customWidth="1"/>
+    <col min="27" max="27" width="50.7777777777778" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="5.77777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="3:27">
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:28">
+      <c r="A2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R2" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="T2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="2:28">
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="P3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="R3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="T3" t="s">
+        <v>56</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="X3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:28">
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R4" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="T4" t="s">
+        <v>56</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="V4" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="X4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:28">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="P5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R5" t="s">
+        <v>56</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="T5" t="s">
+        <v>56</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V5" t="s">
+        <v>56</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="X5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:28">
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R6" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T6" t="s">
+        <v>56</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V6" t="s">
+        <v>56</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:28">
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="P7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R7" t="s">
+        <v>56</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="T7" t="s">
+        <v>56</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V7" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="X7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:28">
+      <c r="A9" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="P9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="T9" t="s">
+        <v>56</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="V9" t="s">
+        <v>56</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="X9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:28">
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="P10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="R10" t="s">
+        <v>56</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="T10" t="s">
+        <v>56</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="V10" t="s">
+        <v>56</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="X10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:28">
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J11" t="s">
+        <v>56</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="N11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="P11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="R11" t="s">
+        <v>56</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="T11" t="s">
+        <v>56</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="V11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="X11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:28">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="J12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="N12" t="s">
+        <v>56</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R12" t="s">
+        <v>56</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="T12" t="s">
+        <v>56</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V12" t="s">
+        <v>56</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="X12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:28">
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N13" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="P13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R13" t="s">
+        <v>56</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="T13" t="s">
+        <v>56</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="V13" t="s">
+        <v>56</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="X13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:28">
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="J14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="L14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N14" t="s">
+        <v>56</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="P14" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R14" t="s">
+        <v>56</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="T14" t="s">
+        <v>56</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V14" t="s">
+        <v>56</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="X14" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:28">
+      <c r="A16" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="N16" t="s">
+        <v>56</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="P16" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="R16" t="s">
+        <v>56</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T16" t="s">
+        <v>56</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="V16" t="s">
+        <v>56</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="X16" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:28">
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J17" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="L17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="N17" t="s">
+        <v>56</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="P17" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="R17" t="s">
+        <v>56</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="T17" t="s">
+        <v>56</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="V17" t="s">
+        <v>56</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="X17" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:28">
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="L18" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="N18" t="s">
+        <v>56</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="P18" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="R18" t="s">
+        <v>56</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="T18" t="s">
+        <v>56</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="V18" t="s">
+        <v>56</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="X18" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:28">
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L19" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="N19" t="s">
+        <v>56</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="P19" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="R19" t="s">
+        <v>56</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="T19" t="s">
+        <v>56</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="V19" t="s">
+        <v>56</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="X19" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:28">
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J20" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L20" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="N20" t="s">
+        <v>56</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="P20" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="R20" t="s">
+        <v>56</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="T20" t="s">
+        <v>56</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="V20" t="s">
+        <v>56</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="X20" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:28">
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H21" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J21" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L21" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="N21" t="s">
+        <v>56</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P21" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="R21" t="s">
+        <v>56</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="T21" t="s">
+        <v>56</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="V21" t="s">
+        <v>56</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X21" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="2:28">
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H22" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="J22" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="L22" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="N22" t="s">
+        <v>56</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="P22" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="R22" t="s">
+        <v>56</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="T22" t="s">
+        <v>56</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="V22" t="s">
+        <v>56</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X22" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:28">
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D23" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="L23" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="N23" t="s">
+        <v>56</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="P23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="R23" t="s">
+        <v>56</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="T23" t="s">
+        <v>56</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="V23" t="s">
+        <v>56</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="X23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:28">
+      <c r="A25" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J25" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L25" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="N25" t="s">
+        <v>56</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="R25" t="s">
+        <v>56</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="T25" t="s">
+        <v>56</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="V25" t="s">
+        <v>56</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="X25" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="2:28">
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J26" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N26" t="s">
+        <v>56</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R26" t="s">
+        <v>56</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="T26" t="s">
+        <v>56</v>
+      </c>
+      <c r="U26" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="V26" t="s">
+        <v>56</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:28">
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N27" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="P27" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R27" t="s">
+        <v>56</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="T27" t="s">
+        <v>56</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="V27" t="s">
+        <v>56</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X27" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:28">
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="L28" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="N28" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="P28" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="R28" t="s">
+        <v>56</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="T28" t="s">
+        <v>56</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="V28" t="s">
+        <v>56</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="X28" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="2:28">
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N29" t="s">
+        <v>56</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="P29" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R29" t="s">
+        <v>56</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="T29" t="s">
+        <v>56</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="V29" t="s">
+        <v>56</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X29" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="2:28">
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H30" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L30" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="N30" t="s">
+        <v>56</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P30" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="R30" t="s">
+        <v>56</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="T30" t="s">
+        <v>56</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="V30" t="s">
+        <v>56</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="X30" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA30" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:28">
+      <c r="A32" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D32" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F32" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H32" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J32" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L32" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="N32" t="s">
+        <v>56</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P32" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="R32" t="s">
+        <v>56</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="T32" t="s">
+        <v>56</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="V32" t="s">
+        <v>56</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="X32" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="2:28">
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D33" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F33" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J33" t="s">
+        <v>56</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L33" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="N33" t="s">
+        <v>56</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="P33" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="R33" t="s">
+        <v>56</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="T33" t="s">
+        <v>56</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="V33" t="s">
+        <v>56</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="X33" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="2:28">
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H34" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L34" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N34" t="s">
+        <v>56</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="P34" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="R34" t="s">
+        <v>56</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="T34" t="s">
+        <v>56</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="V34" t="s">
+        <v>56</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="X34" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="2:28">
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F35" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H35" t="s">
+        <v>56</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J35" t="s">
+        <v>56</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="L35" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="N35" t="s">
+        <v>56</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="P35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="R35" t="s">
+        <v>56</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="T35" t="s">
+        <v>56</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="V35" t="s">
+        <v>56</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="X35" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA35" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="2:28">
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F36" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
+        <v>56</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J36" t="s">
+        <v>56</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36" t="s">
+        <v>56</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P36" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R36" t="s">
+        <v>56</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="T36" t="s">
+        <v>56</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="V36" t="s">
+        <v>56</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X36" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="2:28">
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F37" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H37" t="s">
+        <v>56</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J37" t="s">
+        <v>56</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L37" t="s">
+        <v>56</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="N37" t="s">
+        <v>56</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P37" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="R37" t="s">
+        <v>56</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="T37" t="s">
+        <v>56</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="V37" t="s">
+        <v>56</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="X37" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA37" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:28">
+      <c r="A39" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F39" t="s">
+        <v>56</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" t="s">
+        <v>56</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J39" t="s">
+        <v>56</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="L39" t="s">
+        <v>56</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="N39" t="s">
+        <v>56</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P39" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="R39" t="s">
+        <v>56</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="T39" t="s">
+        <v>56</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="V39" t="s">
+        <v>56</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="X39" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA39" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="2:28">
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H40" t="s">
+        <v>56</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="L40" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="N40" t="s">
+        <v>56</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P40" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="R40" t="s">
+        <v>56</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T40" t="s">
+        <v>56</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="V40" t="s">
+        <v>56</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="X40" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA40" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="2:28">
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F41" t="s">
+        <v>56</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H41" t="s">
+        <v>56</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J41" t="s">
+        <v>56</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L41" t="s">
+        <v>56</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N41" t="s">
+        <v>56</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P41" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="R41" t="s">
+        <v>56</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="T41" t="s">
+        <v>56</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="V41" t="s">
+        <v>56</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="X41" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y41" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA41" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:28">
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D42" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F42" t="s">
+        <v>56</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J42" t="s">
+        <v>56</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="L42" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N42" t="s">
+        <v>56</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="P42" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="R42" t="s">
+        <v>56</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="T42" t="s">
+        <v>56</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="V42" t="s">
+        <v>56</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X42" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y42" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA42" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="2:28">
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D43" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F43" t="s">
+        <v>56</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H43" t="s">
+        <v>56</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J43" t="s">
+        <v>56</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L43" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="N43" t="s">
+        <v>56</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="P43" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="R43" t="s">
+        <v>56</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="T43" t="s">
+        <v>56</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="V43" t="s">
+        <v>56</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="X43" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA43" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:28">
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F44" t="s">
+        <v>56</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="H44" t="s">
+        <v>56</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J44" t="s">
+        <v>56</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="L44" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N44" t="s">
+        <v>56</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="P44" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="R44" t="s">
+        <v>56</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="T44" t="s">
+        <v>56</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="V44" t="s">
+        <v>56</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="X44" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA44" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:28">
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>56</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J45" t="s">
+        <v>56</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L45" t="s">
+        <v>56</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N45" t="s">
+        <v>56</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="P45" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R45" t="s">
+        <v>56</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="T45" t="s">
+        <v>56</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="V45" t="s">
+        <v>56</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="X45" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="2:28">
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D46" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F46" t="s">
+        <v>56</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H46" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J46" t="s">
+        <v>56</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="L46" t="s">
+        <v>56</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="N46" t="s">
+        <v>56</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="P46" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="R46" t="s">
+        <v>56</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="T46" t="s">
+        <v>56</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="V46" t="s">
+        <v>56</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="X46" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y46" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA46" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="2:2">
@@ -1387,802 +9229,802 @@
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>2</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>3</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>4</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>5</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>7</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>8</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>4</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>9</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>7</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>11</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>4</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>12</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>14</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>15</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>16</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" t="s">
-        <v>17</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>20</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>21</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" t="s">
-        <v>22</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" t="s">
-        <v>23</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="3:3">
       <c r="C28" t="s">
-        <v>24</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="3:3">
       <c r="C29" t="s">
-        <v>25</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" spans="3:3">
       <c r="C30" t="s">
-        <v>26</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="3:3">
       <c r="C31" t="s">
-        <v>27</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="3:3">
       <c r="C33" t="s">
-        <v>29</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>30</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="3:3">
       <c r="C35" t="s">
-        <v>22</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" spans="3:3">
       <c r="C36" t="s">
-        <v>31</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" spans="3:3">
       <c r="C37" t="s">
-        <v>32</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38" spans="3:3">
       <c r="C38" t="s">
-        <v>33</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="3:3">
       <c r="C39" t="s">
-        <v>26</v>
+        <v>388</v>
       </c>
     </row>
     <row r="40" spans="3:3">
       <c r="C40" t="s">
-        <v>34</v>
+        <v>395</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="3:3">
       <c r="C42" t="s">
-        <v>36</v>
+        <v>396</v>
       </c>
     </row>
     <row r="43" spans="3:3">
       <c r="C43" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" spans="3:3">
       <c r="C44" t="s">
-        <v>22</v>
+        <v>384</v>
       </c>
     </row>
     <row r="45" spans="3:3">
       <c r="C45" t="s">
-        <v>31</v>
+        <v>392</v>
       </c>
     </row>
     <row r="46" spans="3:3">
       <c r="C46" t="s">
-        <v>32</v>
+        <v>393</v>
       </c>
     </row>
     <row r="47" spans="3:3">
       <c r="C47" t="s">
-        <v>25</v>
+        <v>387</v>
       </c>
     </row>
     <row r="48" spans="3:3">
       <c r="C48" t="s">
-        <v>38</v>
+        <v>398</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>39</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="3:3">
       <c r="C51" t="s">
-        <v>41</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="3:3">
       <c r="C52" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
     </row>
     <row r="53" spans="3:3">
       <c r="C53" t="s">
-        <v>42</v>
+        <v>401</v>
       </c>
     </row>
     <row r="54" spans="3:3">
       <c r="C54" t="s">
-        <v>31</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" spans="3:3">
       <c r="C55" t="s">
-        <v>32</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56" spans="3:3">
       <c r="C56" t="s">
-        <v>25</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" spans="3:3">
       <c r="C57" t="s">
-        <v>38</v>
+        <v>398</v>
       </c>
     </row>
     <row r="58" spans="3:3">
       <c r="C58" t="s">
-        <v>39</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="3:3">
       <c r="C60" t="s">
-        <v>41</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" t="s">
-        <v>37</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" spans="3:3">
       <c r="C62" t="s">
-        <v>42</v>
+        <v>401</v>
       </c>
     </row>
     <row r="63" spans="3:3">
       <c r="C63" t="s">
-        <v>31</v>
+        <v>392</v>
       </c>
     </row>
     <row r="64" spans="3:3">
       <c r="C64" t="s">
-        <v>24</v>
+        <v>386</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" t="s">
-        <v>25</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66" spans="3:3">
       <c r="C66" t="s">
-        <v>44</v>
+        <v>402</v>
       </c>
     </row>
     <row r="67" spans="3:3">
       <c r="C67" t="s">
-        <v>39</v>
+        <v>399</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>45</v>
+        <v>403</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" t="s">
-        <v>48</v>
+        <v>405</v>
       </c>
     </row>
     <row r="72" spans="3:3">
       <c r="C72" t="s">
-        <v>49</v>
+        <v>406</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" t="s">
-        <v>50</v>
+        <v>407</v>
       </c>
     </row>
     <row r="74" spans="3:3">
       <c r="C74" t="s">
-        <v>51</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="3:3">
       <c r="C76" t="s">
-        <v>53</v>
+        <v>409</v>
       </c>
     </row>
     <row r="77" spans="3:3">
       <c r="C77" t="s">
-        <v>54</v>
+        <v>410</v>
       </c>
     </row>
     <row r="78" spans="3:3">
       <c r="C78" t="s">
-        <v>55</v>
+        <v>411</v>
       </c>
     </row>
     <row r="79" spans="3:3">
       <c r="C79" t="s">
-        <v>56</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>58</v>
+        <v>413</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>59</v>
+        <v>414</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>60</v>
+        <v>415</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>61</v>
+        <v>416</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>63</v>
+        <v>417</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>64</v>
+        <v>418</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>65</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>66</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>68</v>
+        <v>421</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>69</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>70</v>
+        <v>419</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>71</v>
+        <v>420</v>
       </c>
     </row>
     <row r="95" spans="2:2">
       <c r="B95" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" spans="3:3">
       <c r="C96" t="s">
-        <v>73</v>
+        <v>423</v>
       </c>
     </row>
     <row r="97" spans="3:3">
       <c r="C97" t="s">
-        <v>74</v>
+        <v>424</v>
       </c>
     </row>
     <row r="98" spans="3:3">
       <c r="C98" t="s">
-        <v>75</v>
+        <v>425</v>
       </c>
     </row>
     <row r="99" spans="3:3">
       <c r="C99" t="s">
-        <v>61</v>
+        <v>416</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="101" spans="3:3">
       <c r="C101" t="s">
-        <v>77</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="3:3">
       <c r="C102" t="s">
-        <v>78</v>
+        <v>427</v>
       </c>
     </row>
     <row r="103" spans="3:3">
       <c r="C103" t="s">
-        <v>79</v>
+        <v>428</v>
       </c>
     </row>
     <row r="104" spans="3:3">
       <c r="C104" t="s">
-        <v>80</v>
+        <v>429</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="106" spans="3:3">
       <c r="C106" t="s">
-        <v>82</v>
+        <v>430</v>
       </c>
     </row>
     <row r="107" spans="3:3">
       <c r="C107" t="s">
-        <v>83</v>
+        <v>431</v>
       </c>
     </row>
     <row r="108" spans="3:3">
       <c r="C108" t="s">
-        <v>84</v>
+        <v>432</v>
       </c>
     </row>
     <row r="109" spans="3:3">
       <c r="C109" t="s">
-        <v>85</v>
+        <v>433</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
     </row>
     <row r="111" spans="3:3">
       <c r="C111" t="s">
-        <v>87</v>
+        <v>434</v>
       </c>
     </row>
     <row r="112" spans="3:3">
       <c r="C112" t="s">
-        <v>88</v>
+        <v>435</v>
       </c>
     </row>
     <row r="113" spans="3:3">
       <c r="C113" t="s">
-        <v>89</v>
+        <v>436</v>
       </c>
     </row>
     <row r="114" spans="3:3">
       <c r="C114" t="s">
-        <v>90</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>91</v>
+        <v>438</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>46</v>
+        <v>404</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
     </row>
     <row r="118" spans="3:3">
       <c r="C118" t="s">
-        <v>93</v>
+        <v>439</v>
       </c>
     </row>
     <row r="119" spans="3:3">
       <c r="C119" t="s">
-        <v>94</v>
+        <v>440</v>
       </c>
     </row>
     <row r="120" spans="3:3">
       <c r="C120" t="s">
-        <v>95</v>
+        <v>441</v>
       </c>
     </row>
     <row r="121" spans="3:3">
       <c r="C121" t="s">
-        <v>96</v>
+        <v>442</v>
       </c>
     </row>
     <row r="122" spans="3:3">
       <c r="C122" t="s">
-        <v>97</v>
+        <v>443</v>
       </c>
     </row>
     <row r="123" spans="3:3">
       <c r="C123" t="s">
-        <v>98</v>
+        <v>444</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
     </row>
     <row r="125" spans="3:3">
       <c r="C125" t="s">
-        <v>100</v>
+        <v>445</v>
       </c>
     </row>
     <row r="126" spans="3:3">
       <c r="C126" t="s">
-        <v>101</v>
+        <v>446</v>
       </c>
     </row>
     <row r="127" spans="3:3">
       <c r="C127" t="s">
-        <v>102</v>
+        <v>447</v>
       </c>
     </row>
     <row r="128" spans="3:3">
       <c r="C128" t="s">
-        <v>103</v>
+        <v>448</v>
       </c>
     </row>
     <row r="129" spans="3:3">
       <c r="C129" t="s">
-        <v>104</v>
+        <v>449</v>
       </c>
     </row>
     <row r="130" spans="3:3">
       <c r="C130" t="s">
-        <v>105</v>
+        <v>450</v>
       </c>
     </row>
     <row r="131" spans="2:2">
       <c r="B131" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
     </row>
     <row r="132" spans="3:3">
       <c r="C132" t="s">
-        <v>107</v>
+        <v>451</v>
       </c>
     </row>
     <row r="133" spans="3:3">
       <c r="C133" t="s">
-        <v>108</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="3:3">
       <c r="C134" t="s">
-        <v>109</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="3:3">
       <c r="C135" t="s">
-        <v>110</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="3:3">
       <c r="C136" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="3:3">
       <c r="C137" t="s">
-        <v>112</v>
+        <v>456</v>
       </c>
     </row>
     <row r="138" spans="3:3">
       <c r="C138" t="s">
-        <v>113</v>
+        <v>457</v>
       </c>
     </row>
     <row r="139" spans="3:3">
       <c r="C139" t="s">
-        <v>114</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>115</v>
+        <v>284</v>
       </c>
     </row>
     <row r="141" spans="3:3">
       <c r="C141" t="s">
-        <v>116</v>
+        <v>459</v>
       </c>
     </row>
     <row r="142" spans="3:3">
       <c r="C142" t="s">
-        <v>117</v>
+        <v>460</v>
       </c>
     </row>
     <row r="143" spans="3:3">
       <c r="C143" t="s">
-        <v>118</v>
+        <v>461</v>
       </c>
     </row>
     <row r="144" spans="3:3">
       <c r="C144" t="s">
-        <v>119</v>
+        <v>462</v>
       </c>
     </row>
     <row r="145" spans="3:3">
       <c r="C145" t="s">
-        <v>120</v>
+        <v>463</v>
       </c>
     </row>
     <row r="146" spans="3:3">
       <c r="C146" t="s">
-        <v>121</v>
+        <v>464</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>122</v>
+        <v>314</v>
       </c>
     </row>
     <row r="148" spans="3:3">
       <c r="C148" t="s">
-        <v>116</v>
+        <v>459</v>
       </c>
     </row>
     <row r="149" spans="3:3">
       <c r="C149" t="s">
-        <v>123</v>
+        <v>465</v>
       </c>
     </row>
     <row r="150" spans="3:3">
       <c r="C150" t="s">
-        <v>124</v>
+        <v>466</v>
       </c>
     </row>
     <row r="151" spans="3:3">
       <c r="C151" t="s">
-        <v>119</v>
+        <v>462</v>
       </c>
     </row>
     <row r="152" spans="3:3">
       <c r="C152" t="s">
-        <v>125</v>
+        <v>467</v>
       </c>
     </row>
     <row r="153" spans="3:3">
       <c r="C153" t="s">
-        <v>126</v>
+        <v>468</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>127</v>
+        <v>336</v>
       </c>
     </row>
     <row r="155" spans="3:3">
       <c r="C155" t="s">
-        <v>128</v>
+        <v>469</v>
       </c>
     </row>
     <row r="156" spans="3:3">
       <c r="C156" t="s">
-        <v>129</v>
+        <v>470</v>
       </c>
     </row>
     <row r="157" spans="3:3">
       <c r="C157" t="s">
-        <v>130</v>
+        <v>471</v>
       </c>
     </row>
     <row r="158" spans="3:3">
       <c r="C158" t="s">
-        <v>131</v>
+        <v>472</v>
       </c>
     </row>
     <row r="159" spans="3:3">
       <c r="C159" t="s">
-        <v>132</v>
+        <v>473</v>
       </c>
     </row>
     <row r="160" spans="3:3">
       <c r="C160" t="s">
-        <v>133</v>
+        <v>474</v>
       </c>
     </row>
     <row r="161" spans="3:3">
       <c r="C161" t="s">
-        <v>134</v>
+        <v>475</v>
       </c>
     </row>
     <row r="162" spans="3:3">
       <c r="C162" t="s">
-        <v>135</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
